--- a/Library_App.xlsx
+++ b/Library_App.xlsx
@@ -357,13 +357,13 @@
     <t>Payment Modes</t>
   </si>
   <si>
-    <t>CASH,UPI,PAYTM,PHONEPAY,GOOGLEPAY,BHIM,CARD,VISA</t>
-  </si>
-  <si>
     <t>Opening Time</t>
   </si>
   <si>
     <t>Closing Time</t>
+  </si>
+  <si>
+    <t>CASH,UPI,CARD</t>
   </si>
 </sst>
 </file>
@@ -1280,10 +1280,10 @@
         <v>97</v>
       </c>
       <c r="E1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F1" t="s">
         <v>103</v>
-      </c>
-      <c r="F1" t="s">
-        <v>104</v>
       </c>
       <c r="G1" t="s">
         <v>101</v>
@@ -1309,7 +1309,7 @@
         <v>0.75</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
